--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/527924_student_fontys_nl/Documents/Documenten/Project_5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_494107901755860E62355476585DCE3A8746CEC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58BC94B7-76AF-4AF5-9489-6B34AC60525A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_494107901755860E62355476585DCE3A8746CEC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7537970C-DB17-49CD-97EA-07A6E9B2F5AB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1254,14 +1254,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D328"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>6</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>6</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>6</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>6</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>6</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>6</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>6</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>6</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>6</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>6</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>6</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>6</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>6</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>6</v>
       </c>
